--- a/1-Processing/Protocol01/Multi/Results/PatientInfos_Summary.xlsx
+++ b/1-Processing/Protocol01/Multi/Results/PatientInfos_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Desktop\Programming\01_Projects\E02_Classification_rTSA\Shoulder_Dev\1-Processing\Protocol01\Multi\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B74B7A-2289-4538-931E-47DBCB32DE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F760194C-6010-4ED5-854C-4DD0F9C8AF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4118" yWindow="593" windowWidth="14400" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PatientInfos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>Hugo Francalanci</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{D19230C7-77F9-4643-8BF1-E3BB50548817}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Patient</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>MB</t>
+  </si>
+  <si>
+    <t>MH</t>
   </si>
   <si>
     <t>Age_PRE</t>
@@ -155,10 +158,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,52 +496,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.73046875" customWidth="1"/>
-    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="2" max="2" width="4.06640625" customWidth="1"/>
     <col min="3" max="3" width="8.265625" customWidth="1"/>
     <col min="4" max="4" width="6.06640625" customWidth="1"/>
     <col min="5" max="5" width="9.46484375" customWidth="1"/>
     <col min="6" max="6" width="10.265625" customWidth="1"/>
-    <col min="7" max="8" width="8.3984375" customWidth="1"/>
+    <col min="7" max="7" width="8.3984375" customWidth="1"/>
+    <col min="8" max="8" width="14.9296875" customWidth="1"/>
     <col min="9" max="9" width="4.46484375" customWidth="1"/>
     <col min="10" max="10" width="8.796875" customWidth="1"/>
     <col min="11" max="11" width="7.73046875" customWidth="1"/>
-    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="12" max="12" width="4.06640625" customWidth="1"/>
     <col min="13" max="13" width="9.33203125" customWidth="1"/>
     <col min="14" max="14" width="6.06640625" customWidth="1"/>
     <col min="15" max="15" width="10.53125" customWidth="1"/>
     <col min="16" max="16" width="11.33203125" customWidth="1"/>
-    <col min="17" max="18" width="9.46484375" customWidth="1"/>
+    <col min="17" max="17" width="9.46484375" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="4.46484375" customWidth="1"/>
     <col min="20" max="20" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -548,28 +553,28 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>1</v>
@@ -578,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" t="s">
         <v>12</v>
-      </c>
-      <c r="N2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
@@ -624,7 +629,7 @@
       <c r="G4">
         <v>22.94</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <f>(1+1.5+1.5+2)/4</f>
         <v>1.5</v>
       </c>
@@ -658,6 +663,64 @@
       </c>
       <c r="T4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>62.3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>156</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="H6">
+        <f>(7+9.5+4+5)/4</f>
+        <v>6.375</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>65.56</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>156</v>
+      </c>
+      <c r="P6">
+        <v>42</v>
+      </c>
+      <c r="Q6">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="R6">
+        <f>(0+0+0+0)/4</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
